--- a/Doc/Skillhub backlog final.xlsx
+++ b/Doc/Skillhub backlog final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tp\skillhub-groupe-DAS\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2472AEA6-1E91-4762-A7E0-E403B91B3E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445ACFA5-EC6E-49D3-BB6D-A12F54C43BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Priorise" sheetId="1" r:id="rId1"/>
@@ -771,16 +771,16 @@
     <t>Steve</t>
   </si>
   <si>
-    <t>Dayab</t>
-  </si>
-  <si>
     <t>Allanah</t>
   </si>
   <si>
-    <t>Steve / Allanah (Tests+TL)</t>
-  </si>
-  <si>
-    <t>Steve / Allanah (Tests)</t>
+    <t>Steve  (Tests+TL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Allanah (Tests)</t>
+  </si>
+  <si>
+    <t>Dayan</t>
   </si>
 </sst>
 </file>
@@ -1122,26 +1122,26 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1425,32 +1425,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -1485,18 +1485,18 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:10" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -1755,18 +1755,18 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
@@ -2057,18 +2057,18 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
     </row>
     <row r="24" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
@@ -2295,18 +2295,18 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
@@ -2528,14 +2528,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="2" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -2562,7 +2562,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>124</v>
@@ -2582,7 +2582,7 @@
         <v>52</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>128</v>
@@ -2853,30 +2853,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -2908,17 +2908,17 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
@@ -3124,17 +3124,17 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="41"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
     </row>
     <row r="13" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
@@ -3369,17 +3369,17 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="40" t="s">
         <v>209</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
     </row>
     <row r="22" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
@@ -3614,17 +3614,17 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
     </row>
     <row r="31" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
@@ -3859,91 +3859,91 @@
       </c>
     </row>
     <row r="40" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
     </row>
     <row r="41" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B41" s="43" t="s">
+      <c r="B41" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="B42" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="B42" s="42" t="s">
         <v>243</v>
       </c>
-      <c r="C42" s="44"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
     </row>
     <row r="43" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="B43" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="B43" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
     </row>
     <row r="44" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="39"/>
+      <c r="G44" s="39"/>
+      <c r="H44" s="39"/>
+      <c r="I44" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="A40:I40"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
